--- a/output/roomself_excel/3840.xlsx
+++ b/output/roomself_excel/3840.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>355326</v>
+        <v>122424</v>
       </c>
       <c r="D2" t="n">
-        <v>6280</v>
+        <v>2828</v>
       </c>
       <c r="E2" t="n">
-        <v>857</v>
+        <v>323</v>
       </c>
       <c r="F2" t="n">
-        <v>639</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -488,17 +488,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>125028</v>
+        <v>170362</v>
       </c>
       <c r="D3" t="n">
-        <v>2916</v>
+        <v>3360</v>
       </c>
       <c r="E3" t="n">
-        <v>453</v>
+        <v>407</v>
       </c>
       <c r="F3" t="n">
         <v>20</v>
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>84636</v>
+        <v>62540</v>
       </c>
       <c r="D4" t="n">
-        <v>2444</v>
+        <v>2028</v>
       </c>
       <c r="E4" t="n">
-        <v>197</v>
+        <v>315</v>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5">
@@ -536,16 +536,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>62712</v>
+        <v>125028</v>
       </c>
       <c r="D5" t="n">
-        <v>2008</v>
+        <v>2916</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>453</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>31800</v>
+        <v>62712</v>
       </c>
       <c r="D6" t="n">
-        <v>1436</v>
+        <v>2008</v>
       </c>
       <c r="E6" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -576,17 +576,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>23600</v>
+        <v>76380</v>
       </c>
       <c r="D7" t="n">
-        <v>1272</v>
+        <v>2212</v>
       </c>
       <c r="E7" t="n">
-        <v>118</v>
+        <v>268</v>
       </c>
       <c r="F7" t="n">
         <v>20</v>
@@ -598,17 +598,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>76380</v>
+        <v>23600</v>
       </c>
       <c r="D8" t="n">
-        <v>2212</v>
+        <v>1272</v>
       </c>
       <c r="E8" t="n">
-        <v>268</v>
+        <v>118</v>
       </c>
       <c r="F8" t="n">
         <v>20</v>
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>41800</v>
+        <v>20500</v>
       </c>
       <c r="D9" t="n">
-        <v>1636</v>
+        <v>1156</v>
       </c>
       <c r="E9" t="n">
-        <v>229</v>
+        <v>125</v>
       </c>
       <c r="F9" t="n">
-        <v>220</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>20500</v>
+        <v>84636</v>
       </c>
       <c r="D10" t="n">
-        <v>1156</v>
+        <v>2444</v>
       </c>
       <c r="E10" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -678,6 +678,50 @@
       </c>
       <c r="F11" t="n">
         <v>20</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>31800</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1436</v>
+      </c>
+      <c r="E12" t="n">
+        <v>159</v>
+      </c>
+      <c r="F12" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>41800</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1636</v>
+      </c>
+      <c r="E13" t="n">
+        <v>229</v>
+      </c>
+      <c r="F13" t="n">
+        <v>220</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/3840.xlsx
+++ b/output/roomself_excel/3840.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,12 +495,20 @@
       <c r="D2" t="n">
         <v>2828</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>323</v>
       </c>
-      <c r="F2" t="n">
-        <v>20</v>
-      </c>
+      <c r="G2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +525,20 @@
       <c r="D3" t="n">
         <v>3360</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>407</v>
       </c>
-      <c r="F3" t="n">
-        <v>20</v>
-      </c>
+      <c r="G3" t="n">
+        <v>20</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,11 +555,27 @@
       <c r="D4" t="n">
         <v>2028</v>
       </c>
-      <c r="E4" t="n">
-        <v>315</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>232</v>
+        <v>212</v>
+      </c>
+      <c r="G4" t="n">
+        <v>20</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>295</v>
+      </c>
+      <c r="J4" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -541,11 +593,27 @@
       <c r="D5" t="n">
         <v>2916</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>453</v>
       </c>
-      <c r="F5" t="n">
-        <v>20</v>
+      <c r="G5" t="n">
+        <v>20</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>276</v>
+      </c>
+      <c r="J5" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -563,12 +631,20 @@
       <c r="D6" t="n">
         <v>2008</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="G6" t="n">
+        <v>19</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,10 +661,26 @@
       <c r="D7" t="n">
         <v>2212</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>285</v>
+      </c>
+      <c r="G7" t="n">
+        <v>19</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>268</v>
       </c>
-      <c r="F7" t="n">
+      <c r="J7" t="n">
         <v>20</v>
       </c>
     </row>
@@ -607,12 +699,20 @@
       <c r="D8" t="n">
         <v>1272</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>118</v>
       </c>
-      <c r="F8" t="n">
-        <v>20</v>
-      </c>
+      <c r="G8" t="n">
+        <v>20</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +729,20 @@
       <c r="D9" t="n">
         <v>1156</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>125</v>
       </c>
-      <c r="F9" t="n">
-        <v>20</v>
-      </c>
+      <c r="G9" t="n">
+        <v>20</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +759,12 @@
       <c r="D10" t="n">
         <v>2444</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +781,20 @@
       <c r="D11" t="n">
         <v>1148</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>123</v>
       </c>
-      <c r="F11" t="n">
-        <v>20</v>
-      </c>
+      <c r="G11" t="n">
+        <v>20</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +811,20 @@
       <c r="D12" t="n">
         <v>1436</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>159</v>
       </c>
-      <c r="F12" t="n">
-        <v>20</v>
-      </c>
+      <c r="G12" t="n">
+        <v>20</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,11 +841,27 @@
       <c r="D13" t="n">
         <v>1636</v>
       </c>
-      <c r="E13" t="n">
-        <v>229</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>220</v>
+        <v>209</v>
+      </c>
+      <c r="G13" t="n">
+        <v>20</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>200</v>
+      </c>
+      <c r="J13" t="n">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
